--- a/python_sql_scripts/results/07_dashboard_views_results.xlsx
+++ b/python_sql_scripts/results/07_dashboard_views_results.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rating_distribution" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="genre_kpis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="movie_popularity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_profiles" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_genres" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content_opportunities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="confusion_matrix" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_metrics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="movie_adjusted_scores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="split_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_profiles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_genres" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content_opportunities" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="opportunity_intervals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="confusion_matrix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_metrics" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -187,7 +189,40 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Result_10" displayName="Result_10" ref="A1:F21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Result_10" displayName="Result_10" ref="A1:J21" headerRowCount="1">
+  <autoFilter ref="A1:J21"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="model_version"/>
+    <tableColumn id="2" name="cluster_id"/>
+    <tableColumn id="3" name="segment_name"/>
+    <tableColumn id="4" name="movie_id"/>
+    <tableColumn id="5" name="title"/>
+    <tableColumn id="6" name="test_support"/>
+    <tableColumn id="7" name="predicted_like_probability"/>
+    <tableColumn id="8" name="actual_positive_rate"/>
+    <tableColumn id="9" name="positive_rate_ci_low"/>
+    <tableColumn id="10" name="positive_rate_ci_high"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Result_11" displayName="Result_11" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="model_version"/>
+    <tableColumn id="2" name="data_split"/>
+    <tableColumn id="3" name="actual_liked"/>
+    <tableColumn id="4" name="predicted_liked"/>
+    <tableColumn id="5" name="row_count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Result_12" displayName="Result_12" ref="A1:F21" headerRowCount="1">
   <autoFilter ref="A1:F21"/>
   <tableColumns count="6">
     <tableColumn id="1" name="model_name"/>
@@ -242,7 +277,25 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Result_05" displayName="Result_05" ref="A1:D4" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Result_05" displayName="Result_05" ref="A1:I21" headerRowCount="1">
+  <autoFilter ref="A1:I21"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="movie_id"/>
+    <tableColumn id="2" name="title"/>
+    <tableColumn id="3" name="genres"/>
+    <tableColumn id="4" name="rating_count"/>
+    <tableColumn id="5" name="avg_rating"/>
+    <tableColumn id="6" name="bayesian_avg_rating"/>
+    <tableColumn id="7" name="positive_rate"/>
+    <tableColumn id="8" name="bayesian_positive_rate"/>
+    <tableColumn id="9" name="wilson_positive_low"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Result_06" displayName="Result_06" ref="A1:D4" headerRowCount="1">
   <autoFilter ref="A1:D4"/>
   <tableColumns count="4">
     <tableColumn id="1" name="data_split"/>
@@ -254,8 +307,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Result_06" displayName="Result_06" ref="A1:H5" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Result_07" displayName="Result_07" ref="A1:H5" headerRowCount="1">
   <autoFilter ref="A1:H5"/>
   <tableColumns count="8">
     <tableColumn id="1" name="cluster_id"/>
@@ -271,8 +324,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Result_07" displayName="Result_07" ref="A1:G21" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Result_08" displayName="Result_08" ref="A1:G21" headerRowCount="1">
   <autoFilter ref="A1:G21"/>
   <tableColumns count="7">
     <tableColumn id="1" name="cluster_id"/>
@@ -287,8 +340,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Result_08" displayName="Result_08" ref="A1:K21" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Result_09" displayName="Result_09" ref="A1:K21" headerRowCount="1">
   <autoFilter ref="A1:K21"/>
   <tableColumns count="11">
     <tableColumn id="1" name="model_version"/>
@@ -302,20 +355,6 @@
     <tableColumn id="9" name="actual_positive_rate"/>
     <tableColumn id="10" name="train_popularity"/>
     <tableColumn id="11" name="train_avg_rating"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Result_09" displayName="Result_09" ref="A1:E5" headerRowCount="1">
-  <autoFilter ref="A1:E5"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="model_version"/>
-    <tableColumn id="2" name="data_split"/>
-    <tableColumn id="3" name="actual_liked"/>
-    <tableColumn id="4" name="predicted_liked"/>
-    <tableColumn id="5" name="row_count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -687,6 +726,982 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model_version</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>segment_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>test_support</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_like_probability</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>actual_positive_rate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>positive_rate_ci_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>positive_rate_ci_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>356</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Forrest Gump (1994)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.637271559623</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.4509363099736562</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0.7073878752583377</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1258</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Shining, The (1980)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.694923317925</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.5259683241967119</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.773150631176808</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1959</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Out of Africa (1985)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.47776686</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.1250102748137801</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.5087528193979559</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Gods Must Be Crazy, The (1980)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.515091241</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.3420820083075996</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.741804979142907</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2202</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Lifeboat (1944)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.658687234286</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.3258787516087127</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.7861739790880858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Blair Witch Project, The (1999)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.290781749167</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.2115913343900347</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.5729038094433627</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3101</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Fatal Attraction (1987)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.452812213043</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.1880908756453528</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.5510751947178765</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3219</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Pacific Heights (1990)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.358290588</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.03622316096978746</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.6244717358814612</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4361</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Tootsie (1982)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.6098121508</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.3706701701956442</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0.7333462505299742</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4546</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Vanishing, The (Spoorloos) (1988)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.696154884444</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.4526042641652114</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.9367864660831658</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5299</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>My Big Fat Greek Wedding (2002)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.505559721489</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.2216511802889302</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.4832676262995561</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>6993</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Hannah and Her Sisters (1986)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.583354728966</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.440032170834645</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.7731304026757028</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>8132</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Gladiator (1992)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.397904573056</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.5033703772392374</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.7978825836158739</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8464</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Super Size Me (2004)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.632266444</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.4065267362417985</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.6036612817659347</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Selective Critics</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8781</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Manchurian Candidate, The (2004)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.397411460909</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.1282980359809725</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0.4102236341899661</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Mainstream Enthusiasts</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Shawshank Redemption, The (1994)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.682788846957</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.3680948502682136</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.7436421550689576</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Mainstream Enthusiasts</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>745</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Wallace &amp; Gromit: A Close Shave (1995)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.713744293333</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.4364603291452128</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.9699370047868296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Mainstream Enthusiasts</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Strangelove or: How I Learned to Stop Worrying and Love the Bomb (1964)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.673936369231</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.3552380217738891</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.8229160728912626</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Mainstream Enthusiasts</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Godfather, The (1972)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.707681777</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.3126695474501864</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.8318224187964903</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Mainstream Enthusiasts</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>898</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia Story, The (1940)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.793490465</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.09452865480086611</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.905471345199134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model_version</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>data_split</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>actual_liked</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_liked</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>row_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>21802</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>14189</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>31273</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>logit_v1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>9369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2355,6 +3370,741 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>genres</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>rating_count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>avg_rating</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bayesian_avg_rating</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>positive_rate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bayesian_positive_rate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>wilson_positive_low</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Toy Story (1995)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Adventure|Animation|Children|Comedy|Fantasy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>19868</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4.000679484</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3.9983004157</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.716881417</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.7158934300000001</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0.7105754487937852</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Jumanji (1995)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Adventure|Children|Fantasy</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8969</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3.306054186</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3.3084753225</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.391124986</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.39254163</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.3810740129195418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Grumpier Old Men (1995)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Romance</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6690</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3.195889387</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>3.2007456112</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.338116591</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.3407894</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.3268761815749802</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Waiting to Exhale (1995)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Drama|Romance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2.88379657</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2.9196329983</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.2578356</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.27245114</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.2375509244436812</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Father of the Bride Part II (1995)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3.137302355</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>3.1434681963</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.291545659</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.29516672</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.2803629414381847</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Heat (1995)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Action|Crime|Thriller</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>11293</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3.793367572</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>3.7910175283</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.613565925</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.61274116</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.6045478521466756</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Sabrina (1995)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Romance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7033</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3.423005829</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3.4244445114</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.430826105</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.43207066</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.4192936122559255</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Tom and Huck (1995)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Adventure|Children</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3.159254807</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>3.1985651288</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.323317307</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.34437768</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.2924086053461977</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sudden Death (1995)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2354</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3.036108751</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3.05605652</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.270178419</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.2803423</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.2526250559024152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>GoldenEye (1995)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Action|Adventure|Thriller</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>13851</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>3.440148725</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>3.4407614293</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.438235506</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.43881872</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.4299905940095509</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>American President, The (1995)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Drama|Romance</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9940</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3.722736418</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>3.7207731773</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.593661971</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.5929243</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.5839720517008061</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Dracula: Dead and Loving It (1995)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Horror</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2.560030395</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.6065876085</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.166666666</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.1836837</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.15087677719287</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Balto (1995)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Animation|Children</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3.230029585</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3.2681220361</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.353550295</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.37494845</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.3184310377348447</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Nixon (1995)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3459</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>3.444926279</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>3.4471937904</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.46776525</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.46922169</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.4511819544088495</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Cutthroat Island (1995)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Action|Adventure|Romance</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1585</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2.756782334</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2.8024110979</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.218927444</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.23677151</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.1992622119482839</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Casino (1995)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Crime|Drama</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>7214</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3.719503742</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3.7168529806</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.5916273909999999</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.5906426</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.5802387332684953</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Sense and Sensibility (1995)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Drama|Romance</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11161</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>4.001299166</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3.9970750999</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.72224711</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.72044756</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.71386218217678</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Four Rooms (1995)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Comedy|Drama|Thriller</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2336</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>3.282320205</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3.2923081691</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.407106164</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.41172414</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.38735112531608</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Ace Ventura: When Nature Calls (1995)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>8440</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2.573578199</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2.5847263115</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.168838862</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.17294614</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.1609977729979748</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Money Train (1995)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Action|Comedy|Crime|Drama|Thriller</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2074</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2.901157184</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.9298816467</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.218418514</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.23227231</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.2011658126256844</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2442,7 +4192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2623,7 +4373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3226,7 +4976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4171,139 +5921,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model_version</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>data_split</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>actual_liked</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predicted_liked</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>row_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>logit_v1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>21802</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>logit_v1</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>14189</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>logit_v1</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>31273</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>logit_v1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9369</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>